--- a/tests/fixtures/template_fixture_alt.xlsx
+++ b/tests/fixtures/template_fixture_alt.xlsx
@@ -16,8 +16,7 @@
     <sheet name="Contact people" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="Interfaces" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="Vendor info" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Notes" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Accounts" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Accounts" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191028" fullCalcOnLoad="1"/>
@@ -776,48 +775,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16.140625" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>ORG CODE</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>NOTE</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="n"/>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ACME</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>a dropped note</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/tests/fixtures/template_fixture_alt.xlsx
+++ b/tests/fixtures/template_fixture_alt.xlsx
@@ -1148,7 +1148,7 @@
       </c>
       <c r="H1" s="2" t="inlineStr">
         <is>
-          <t>CATEGORY</t>
+          <t>CATEGORIES</t>
         </is>
       </c>
       <c r="I1" s="28" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <t>CATEGORY</t>
+          <t>CATEGORIES</t>
         </is>
       </c>
       <c r="E1" s="28" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <t>CATEGORY</t>
+          <t>CATEGORIES</t>
         </is>
       </c>
       <c r="E1" s="28" t="inlineStr">
@@ -1418,13 +1418,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.140625" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -1446,10 +1446,15 @@
       </c>
       <c r="D1" s="28" t="inlineStr">
         <is>
-          <t>CATEGORY</t>
+          <t>NOTE</t>
         </is>
       </c>
       <c r="E1" s="28" t="inlineStr">
+        <is>
+          <t>CATEGORIES</t>
+        </is>
+      </c>
+      <c r="F1" s="28" t="inlineStr">
         <is>
           <t>IS PRIMARY</t>
         </is>
@@ -1473,10 +1478,15 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>vendor note</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>Support</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -1491,6 +1501,11 @@
       <c r="B3" t="inlineStr">
         <is>
           <t>https://support.acme.example</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>second url note</t>
         </is>
       </c>
     </row>
@@ -1567,7 +1582,7 @@
       </c>
       <c r="I1" s="4" t="inlineStr">
         <is>
-          <t>CATEGORY</t>
+          <t>CATEGORIES</t>
         </is>
       </c>
     </row>

--- a/tests/fixtures/template_fixture_alt.xlsx
+++ b/tests/fixtures/template_fixture_alt.xlsx
@@ -17,6 +17,7 @@
     <sheet name="Interfaces" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="Vendor info" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="Accounts" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="External note" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191028" fullCalcOnLoad="1"/>
@@ -885,6 +886,87 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10.57" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15.75" customHeight="1">
+      <c r="A1" s="31" t="inlineStr">
+        <is>
+          <t>ORG CODE</t>
+        </is>
+      </c>
+      <c r="B1" s="31" t="inlineStr">
+        <is>
+          <t>NOTE TYPE</t>
+        </is>
+      </c>
+      <c r="C1" s="31" t="inlineStr">
+        <is>
+          <t>NOTE TITLE</t>
+        </is>
+      </c>
+      <c r="D1" s="28" t="inlineStr">
+        <is>
+          <t>CONTENTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ACME</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>first note</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>first note body</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ACME</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Follow-up</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>second note</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/tests/fixtures/template_fixture_alt.xlsx
+++ b/tests/fixtures/template_fixture_alt.xlsx
@@ -686,80 +686,81 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1"/>
+  <dimension ref="A2:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14.42578125" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="14"/>
   </cols>
   <sheetData>
-    <row r="1" ht="45" customHeight="1">
-      <c r="A1" s="9" t="inlineStr">
+    <row r="1" ht="45" customHeight="1"/>
+    <row r="2">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>ORG CODE</t>
         </is>
       </c>
-      <c r="B1" s="27" t="inlineStr">
+      <c r="B2" s="27" t="inlineStr">
         <is>
           <t>PAYMENT METHOD</t>
         </is>
       </c>
-      <c r="C1" s="27" t="inlineStr">
+      <c r="C2" s="27" t="inlineStr">
         <is>
           <t>CURRENCIES</t>
         </is>
       </c>
-      <c r="D1" s="27" t="inlineStr">
+      <c r="D2" s="27" t="inlineStr">
         <is>
           <t>CLAIMING INTERVAL</t>
         </is>
       </c>
-      <c r="E1" s="27" t="inlineStr">
+      <c r="E2" s="27" t="inlineStr">
         <is>
           <t>DISCOUNT %</t>
         </is>
       </c>
-      <c r="F1" s="27" t="inlineStr">
+      <c r="F2" s="27" t="inlineStr">
         <is>
           <t>EXP ACTIVATION INTERVAL</t>
         </is>
       </c>
-      <c r="G1" s="27" t="inlineStr">
+      <c r="G2" s="27" t="inlineStr">
         <is>
           <t>EXP INVOICE INTERVAL</t>
         </is>
       </c>
-      <c r="H1" s="27" t="inlineStr">
+      <c r="H2" s="27" t="inlineStr">
         <is>
           <t>EXP RECEIPT INTERVAL</t>
         </is>
       </c>
-      <c r="I1" s="27" t="inlineStr">
+      <c r="I2" s="27" t="inlineStr">
         <is>
           <t>RENEWAL ACTIVATION INTERVAL</t>
         </is>
       </c>
-      <c r="J1" s="27" t="inlineStr">
+      <c r="J2" s="27" t="inlineStr">
         <is>
           <t>SUBSCRIPTION INTERVAL</t>
         </is>
       </c>
-      <c r="K1" s="27" t="inlineStr">
+      <c r="K2" s="27" t="inlineStr">
         <is>
           <t>EXPORT TO ACCOUNTING (Y/)</t>
         </is>
       </c>
-      <c r="L1" s="27" t="inlineStr">
+      <c r="L2" s="27" t="inlineStr">
         <is>
           <t>TAX ID</t>
         </is>
       </c>
-      <c r="M1" s="27" t="inlineStr">
+      <c r="M2" s="27" t="inlineStr">
         <is>
           <t>TAX %</t>
         </is>
       </c>
-      <c r="N1" s="27" t="inlineStr">
+      <c r="N2" s="27" t="inlineStr">
         <is>
           <t>LIABLE FOR VAT (Y/N)</t>
         </is>
@@ -776,7 +777,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A2:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.28515625" customWidth="1" style="20" min="1" max="1"/>
@@ -789,97 +790,98 @@
     <col width="20" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" s="24">
-      <c r="A1" s="29" t="inlineStr">
+    <row r="1" customFormat="1" s="24"/>
+    <row r="2">
+      <c r="A2" s="29" t="inlineStr">
         <is>
           <t>ORG CODE</t>
         </is>
       </c>
-      <c r="B1" s="22" t="inlineStr">
+      <c r="B2" s="22" t="inlineStr">
         <is>
           <t>ACCOUNT NAME</t>
         </is>
       </c>
-      <c r="C1" s="30" t="inlineStr">
+      <c r="C2" s="30" t="inlineStr">
         <is>
           <t>ACCOUNT NUMBER</t>
         </is>
       </c>
-      <c r="D1" s="23" t="inlineStr">
+      <c r="D2" s="23" t="inlineStr">
         <is>
           <t>DESCRIPTION</t>
         </is>
       </c>
-      <c r="E1" s="23" t="inlineStr">
+      <c r="E2" s="23" t="inlineStr">
         <is>
           <t>ACCOUNTING CODE</t>
         </is>
       </c>
-      <c r="F1" s="23" t="inlineStr">
+      <c r="F2" s="23" t="inlineStr">
         <is>
           <t>PAYMENT METHOD</t>
         </is>
       </c>
-      <c r="G1" s="30" t="inlineStr">
+      <c r="G2" s="30" t="inlineStr">
         <is>
           <t>ACCOUNT STATUS</t>
         </is>
       </c>
-      <c r="H1" s="26" t="inlineStr">
+      <c r="H2" s="26" t="inlineStr">
         <is>
           <t>LIBRARY EDI CODE</t>
         </is>
       </c>
-      <c r="I1" s="23" t="inlineStr">
+      <c r="I2" s="23" t="inlineStr">
         <is>
           <t>NOTES</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="19" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="19" t="inlineStr">
         <is>
           <t>ACME</t>
         </is>
       </c>
-      <c r="B2" s="10" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>Main Account</t>
         </is>
       </c>
-      <c r="C2" s="25" t="inlineStr">
+      <c r="C3" s="25" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="D2" s="18" t="n"/>
-      <c r="E2" s="18" t="inlineStr">
+      <c r="D3" s="18" t="n"/>
+      <c r="E3" s="18" t="inlineStr">
         <is>
           <t>SYS1</t>
         </is>
       </c>
-      <c r="F2" s="18" t="n"/>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="F3" s="18" t="n"/>
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H2" s="25" t="n"/>
-      <c r="I2" t="inlineStr">
+      <c r="H3" s="25" t="n"/>
+      <c r="I3" t="inlineStr">
         <is>
           <t>acct note</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="19" t="n"/>
-      <c r="B3" s="10" t="n"/>
-      <c r="C3" s="25" t="n"/>
-      <c r="D3" s="5" t="n"/>
-      <c r="E3" s="5" t="n"/>
-      <c r="F3" s="5" t="n"/>
-      <c r="G3" s="5" t="n"/>
-      <c r="H3" s="25" t="n"/>
+    <row r="4">
+      <c r="A4" s="19" t="n"/>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="25" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="25" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -892,7 +894,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A2:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.57" customWidth="1" min="1" max="1"/>
@@ -901,47 +903,26 @@
     <col width="50" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="31" t="inlineStr">
+    <row r="1" ht="15.75" customHeight="1"/>
+    <row r="2">
+      <c r="A2" s="31" t="inlineStr">
         <is>
           <t>ORG CODE</t>
         </is>
       </c>
-      <c r="B1" s="31" t="inlineStr">
+      <c r="B2" s="31" t="inlineStr">
         <is>
           <t>NOTE TYPE</t>
         </is>
       </c>
-      <c r="C1" s="31" t="inlineStr">
+      <c r="C2" s="31" t="inlineStr">
         <is>
           <t>NOTE TITLE</t>
         </is>
       </c>
-      <c r="D1" s="28" t="inlineStr">
+      <c r="D2" s="28" t="inlineStr">
         <is>
           <t>CONTENTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ACME</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>first note</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>first note body</t>
         </is>
       </c>
     </row>
@@ -953,10 +934,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>first note</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>first note body</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ACME</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>Follow-up</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>second note</t>
         </is>
@@ -1106,7 +1109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A2:C5"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="7.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="15.42578125" customWidth="1" min="1" max="1"/>
@@ -1114,32 +1117,21 @@
     <col width="13.28515625" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="9" t="inlineStr">
+    <row r="1" ht="15.75" customHeight="1"/>
+    <row r="2">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>ORG CODE</t>
         </is>
       </c>
-      <c r="B1" s="13" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>ALT NAME</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Description</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ACME</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>AcmeAlias</t>
         </is>
       </c>
     </row>
@@ -1151,12 +1143,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Acme Corp</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Formal name</t>
+          <t>AcmeAlias</t>
         </is>
       </c>
     </row>
@@ -1167,6 +1154,23 @@
         </is>
       </c>
       <c r="B4" t="inlineStr">
+        <is>
+          <t>Acme Corp</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Formal name</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ACME</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
         <is>
           <t>Acme Inc</t>
         </is>
@@ -1183,7 +1187,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A2:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20.28515625" customWidth="1" min="1" max="1"/>
@@ -1192,87 +1196,51 @@
     <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="9" t="inlineStr">
+    <row r="1" ht="15.75" customHeight="1"/>
+    <row r="2">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>ORG CODE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ADDR1 </t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>ADDR2</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>CITY</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>REGION</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>POSTAL CODE</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>COUNTRY</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>CATEGORIES</t>
         </is>
       </c>
-      <c r="I1" s="28" t="inlineStr">
+      <c r="I2" s="28" t="inlineStr">
         <is>
           <t>IS PRIMARY</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ACME</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>1 Main St</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Springfield</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>IL</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>62701</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1284,10 +1252,47 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>1 Main St</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Springfield</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>62701</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ACME</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>2 Warehouse Rd</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>Billing</t>
         </is>
@@ -1309,7 +1314,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A2:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16.7109375" customWidth="1" min="1" max="1"/>
@@ -1318,49 +1323,31 @@
     <col width="14" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="9" t="inlineStr">
+    <row r="1" ht="15.75" customHeight="1"/>
+    <row r="2">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>ORG CODE</t>
         </is>
       </c>
-      <c r="B1" s="13" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>PHONE</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>TYPE</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>CATEGORIES</t>
         </is>
       </c>
-      <c r="E1" s="28" t="inlineStr">
+      <c r="E2" s="28" t="inlineStr">
         <is>
           <t>IS PRIMARY</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>ACME</t>
-        </is>
-      </c>
-      <c r="B2" s="10" t="inlineStr">
-        <is>
-          <t>555-1000</t>
-        </is>
-      </c>
-      <c r="C2" s="5" t="n"/>
-      <c r="D2" s="5" t="n"/>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1372,28 +1359,47 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
+          <t>555-1000</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>ACME</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
           <t>555-2000</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>Fax</t>
         </is>
       </c>
-      <c r="D3" s="5" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="D4" s="5" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>ACME</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>555-3000</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Mobile</t>
         </is>
@@ -1418,7 +1424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A2:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.140625" customWidth="1" min="1" max="1"/>
@@ -1428,47 +1434,31 @@
     <col width="14" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="9" t="inlineStr">
+    <row r="1" ht="15.75" customHeight="1"/>
+    <row r="2">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>ORG CODE</t>
         </is>
       </c>
-      <c r="B1" s="13" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>EMAIL</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>DESCRIPTION</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>CATEGORIES</t>
         </is>
       </c>
-      <c r="E1" s="28" t="inlineStr">
+      <c r="E2" s="28" t="inlineStr">
         <is>
           <t>IS PRIMARY</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>ACME</t>
-        </is>
-      </c>
-      <c r="B2" s="10" t="inlineStr">
-        <is>
-          <t>info@acme.example</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1479,6 +1469,23 @@
         </is>
       </c>
       <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>info@acme.example</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>ACME</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>sales@acme.example</t>
         </is>
@@ -1500,7 +1507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A2:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.140625" customWidth="1" min="1" max="1"/>
@@ -1510,67 +1517,35 @@
     <col width="14" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="31" t="inlineStr">
+    <row r="2">
+      <c r="A2" s="31" t="inlineStr">
         <is>
           <t>ORG CODE</t>
         </is>
       </c>
-      <c r="B1" s="31" t="inlineStr">
+      <c r="B2" s="31" t="inlineStr">
         <is>
           <t>URL</t>
         </is>
       </c>
-      <c r="C1" s="28" t="inlineStr">
+      <c r="C2" s="28" t="inlineStr">
         <is>
           <t>DESCRIPTION</t>
         </is>
       </c>
-      <c r="D1" s="28" t="inlineStr">
+      <c r="D2" s="28" t="inlineStr">
         <is>
           <t>NOTE</t>
         </is>
       </c>
-      <c r="E1" s="28" t="inlineStr">
+      <c r="E2" s="28" t="inlineStr">
         <is>
           <t>CATEGORIES</t>
         </is>
       </c>
-      <c r="F1" s="28" t="inlineStr">
+      <c r="F2" s="28" t="inlineStr">
         <is>
           <t>IS PRIMARY</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ACME</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>https://acme.example</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Main website</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>vendor note</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Support</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1582,10 +1557,42 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>https://acme.example</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Main website</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>vendor note</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ACME</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>https://support.acme.example</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>second url note</t>
         </is>
@@ -1607,7 +1614,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A2:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="20.25" customHeight="1"/>
   <cols>
     <col width="10.28515625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1621,104 +1628,105 @@
     <col width="13" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20.25" customFormat="1" customHeight="1" s="3">
-      <c r="A1" s="9" t="inlineStr">
+    <row r="1" ht="20.25" customFormat="1" customHeight="1" s="3"/>
+    <row r="2" ht="20.25" customHeight="1">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>ORG CODE</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B2" s="9" t="inlineStr">
         <is>
           <t>LAST NAME</t>
         </is>
       </c>
-      <c r="C1" s="9" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>FIRST NAME</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D2" s="1" t="inlineStr">
         <is>
           <t>TITLE</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E2" s="1" t="inlineStr">
         <is>
           <t>NOTES</t>
         </is>
       </c>
-      <c r="F1" s="9" t="inlineStr">
+      <c r="F2" s="9" t="inlineStr">
         <is>
           <t>EMAIL</t>
         </is>
       </c>
-      <c r="G1" s="9" t="inlineStr">
+      <c r="G2" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">PHONE </t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H2" s="1" t="inlineStr">
         <is>
           <t>DESCRIPTION</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="I2" s="4" t="inlineStr">
         <is>
           <t>CATEGORIES</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="20.25" customHeight="1">
-      <c r="A2" s="5" t="inlineStr">
+    <row r="3" ht="20.25" customHeight="1">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>ACME</t>
         </is>
       </c>
-      <c r="B2" s="10" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>Smith</t>
         </is>
       </c>
-      <c r="C2" s="10" t="inlineStr">
+      <c r="C3" s="10" t="inlineStr">
         <is>
           <t>Jo</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>a note</t>
         </is>
       </c>
-      <c r="F2" s="10" t="inlineStr">
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>jo@acme.example</t>
         </is>
       </c>
-      <c r="G2" s="10" t="inlineStr">
+      <c r="G3" s="10" t="inlineStr">
         <is>
           <t>555-4000</t>
         </is>
       </c>
-      <c r="H2" s="5" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>main contact</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="20.25" customHeight="1">
-      <c r="A3" s="5" t="n"/>
-      <c r="B3" s="10" t="n"/>
-      <c r="C3" s="10" t="n"/>
-      <c r="D3" s="5" t="n"/>
-      <c r="E3" s="5" t="n"/>
-      <c r="F3" s="10" t="n"/>
-      <c r="G3" s="10" t="n"/>
-      <c r="H3" s="5" t="n"/>
+    <row r="4">
+      <c r="A4" s="5" t="n"/>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="10" t="n"/>
+      <c r="G4" s="10" t="n"/>
+      <c r="H4" s="5" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1731,7 +1739,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A2:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.5703125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1743,98 +1751,99 @@
     <col width="13.140625" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="9" t="inlineStr">
+    <row r="1" ht="15.75" customHeight="1"/>
+    <row r="2">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>ORG CODE</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B2" s="9" t="inlineStr">
         <is>
           <t>NAME</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>TYPE</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>URL</t>
         </is>
       </c>
-      <c r="E1" s="28" t="inlineStr">
+      <c r="E2" s="28" t="inlineStr">
         <is>
           <t>DELIVERY METHOD</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>USERNAME</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>PASSWORD</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>DESCRIPTION</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>NOTES</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>ACME</t>
         </is>
       </c>
-      <c r="B2" s="10" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>Acme Admin</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Admin</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="D3" s="6" t="inlineStr">
         <is>
           <t>https://admin.acme.example</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>user</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
-      <c r="H2" s="5" t="n"/>
-      <c r="I2" t="inlineStr">
+      <c r="H3" s="5" t="n"/>
+      <c r="I3" t="inlineStr">
         <is>
           <t>iface note</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="5" t="n"/>
-      <c r="B3" s="10" t="n"/>
-      <c r="D3" s="5" t="n"/>
-      <c r="F3" s="5" t="n"/>
-      <c r="G3" s="5" t="n"/>
-      <c r="H3" s="5" t="n"/>
+    <row r="4">
+      <c r="A4" s="5" t="n"/>
+      <c r="B4" s="10" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="2">

--- a/tests/fixtures/template_fixture_alt.xlsx
+++ b/tests/fixtures/template_fixture_alt.xlsx
@@ -686,7 +686,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:N2"/>
+  <dimension ref="A2:N3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14.42578125" customWidth="1" min="1" max="1"/>
@@ -697,7 +697,7 @@
     <row r="2">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t>ORG CODE</t>
+          <t>ORG CODE*</t>
         </is>
       </c>
       <c r="B2" s="27" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="F2" s="27" t="inlineStr">
         <is>
-          <t>EXP ACTIVATION INTERVAL</t>
+          <t>EXPECTED ACTIVATION INTERVAL</t>
         </is>
       </c>
       <c r="G2" s="27" t="inlineStr">
@@ -763,6 +763,50 @@
       <c r="N2" s="27" t="inlineStr">
         <is>
           <t>LIABLE FOR VAT (Y/N)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ACME</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>EFT</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" t="n">
+        <v>15</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>12-345</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -794,17 +838,17 @@
     <row r="2">
       <c r="A2" s="29" t="inlineStr">
         <is>
-          <t>ORG CODE</t>
+          <t>ORG CODE*</t>
         </is>
       </c>
       <c r="B2" s="22" t="inlineStr">
         <is>
-          <t>ACCOUNT NAME</t>
+          <t>ACCOUNT NAME*</t>
         </is>
       </c>
       <c r="C2" s="30" t="inlineStr">
         <is>
-          <t>ACCOUNT NUMBER</t>
+          <t>ACCOUNT NUMBER*</t>
         </is>
       </c>
       <c r="D2" s="23" t="inlineStr">
@@ -824,7 +868,7 @@
       </c>
       <c r="G2" s="30" t="inlineStr">
         <is>
-          <t>ACCOUNT STATUS</t>
+          <t>ACCOUNT STATUS*</t>
         </is>
       </c>
       <c r="H2" s="26" t="inlineStr">
@@ -907,17 +951,17 @@
     <row r="2">
       <c r="A2" s="31" t="inlineStr">
         <is>
-          <t>ORG CODE</t>
+          <t>ORG CODE*</t>
         </is>
       </c>
       <c r="B2" s="31" t="inlineStr">
         <is>
-          <t>NOTE TYPE</t>
+          <t>NOTE TYPE*</t>
         </is>
       </c>
       <c r="C2" s="31" t="inlineStr">
         <is>
-          <t>NOTE TITLE</t>
+          <t>NOTE TITLE*</t>
         </is>
       </c>
       <c r="D2" s="28" t="inlineStr">
@@ -1015,12 +1059,12 @@
     <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>ORG CODE</t>
+          <t>ORG CODE*</t>
         </is>
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>ORG NAME</t>
+          <t>ORG NAME*</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -1030,7 +1074,7 @@
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>ORG status (Active/Inactive/Pending)</t>
+          <t>ORG status (Active/Inactive/Pending)*</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -1038,7 +1082,11 @@
           <t>Description</t>
         </is>
       </c>
-      <c r="F5" s="2" t="n"/>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>ORG TYPE (Choose one or create your own)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
@@ -1064,6 +1112,11 @@
       <c r="E6" s="5" t="inlineStr">
         <is>
           <t>A test vendor</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vendor</t>
         </is>
       </c>
     </row>
@@ -1121,12 +1174,12 @@
     <row r="2">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t>ORG CODE</t>
+          <t>ORG CODE*</t>
         </is>
       </c>
       <c r="B2" s="13" t="inlineStr">
         <is>
-          <t>ALT NAME</t>
+          <t>ALT NAME*</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -1200,7 +1253,7 @@
     <row r="2">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t>ORG CODE</t>
+          <t>ORG CODE*</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -1327,12 +1380,12 @@
     <row r="2">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t>ORG CODE</t>
+          <t>ORG CODE*</t>
         </is>
       </c>
       <c r="B2" s="13" t="inlineStr">
         <is>
-          <t>PHONE</t>
+          <t>PHONE*</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -1424,7 +1477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:E4"/>
+  <dimension ref="A2:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.140625" customWidth="1" min="1" max="1"/>
@@ -1438,12 +1491,12 @@
     <row r="2">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t>ORG CODE</t>
+          <t>ORG CODE*</t>
         </is>
       </c>
       <c r="B2" s="13" t="inlineStr">
         <is>
-          <t>EMAIL</t>
+          <t>EMAIL*</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -1451,12 +1504,17 @@
           <t>DESCRIPTION</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>LANGUAGE</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>CATEGORIES</t>
         </is>
       </c>
-      <c r="E2" s="28" t="inlineStr">
+      <c r="F2" s="28" t="inlineStr">
         <is>
           <t>IS PRIMARY</t>
         </is>
@@ -1473,7 +1531,12 @@
           <t>info@acme.example</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>eng</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -1520,12 +1583,12 @@
     <row r="2">
       <c r="A2" s="31" t="inlineStr">
         <is>
-          <t>ORG CODE</t>
+          <t>ORG CODE*</t>
         </is>
       </c>
       <c r="B2" s="31" t="inlineStr">
         <is>
-          <t>URL</t>
+          <t>URL*</t>
         </is>
       </c>
       <c r="C2" s="28" t="inlineStr">
@@ -1632,17 +1695,17 @@
     <row r="2" ht="20.25" customHeight="1">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t>ORG CODE</t>
+          <t>ORG CODE*</t>
         </is>
       </c>
       <c r="B2" s="9" t="inlineStr">
         <is>
-          <t>LAST NAME</t>
+          <t>LAST NAME*</t>
         </is>
       </c>
       <c r="C2" s="9" t="inlineStr">
         <is>
-          <t>FIRST NAME</t>
+          <t>FIRST NAME*</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
@@ -1755,7 +1818,7 @@
     <row r="2">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t>ORG CODE</t>
+          <t>ORG CODE*</t>
         </is>
       </c>
       <c r="B2" s="9" t="inlineStr">
